--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$47</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -418,38 +421,65 @@
     <t>Practitioner.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Practitioner.extension:ClinicianUserIndex</t>
+  </si>
+  <si>
+    <t>ClinicianUserIndex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/clinician-user-index}
+</t>
+  </si>
+  <si>
+    <t>Requesting Clinician</t>
+  </si>
+  <si>
+    <t>The user index for the person who is requesting or performing the service request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Practitioner.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Practitioner.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -572,17 +602,13 @@
     <t>Practitioner.name.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -846,6 +872,9 @@
   </si>
   <si>
     <t>Practitioner.telecom.system.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Practitioner.telecom.system.value</t>
@@ -1320,6 +1349,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1493,12 +1537,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.07421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1506,7 +1550,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.67578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1659,7 +1703,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>9</v>
       </c>
@@ -1771,7 +1815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -1885,7 +1929,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>93</v>
       </c>
@@ -1997,7 +2041,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>99</v>
       </c>
@@ -2111,7 +2155,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>105</v>
       </c>
@@ -2225,7 +2269,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>114</v>
       </c>
@@ -2339,7 +2383,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2453,7 +2497,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>130</v>
       </c>
@@ -2462,11 +2506,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -2481,17 +2525,15 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -2528,16 +2570,14 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -2558,7 +2598,7 @@
         <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>76</v>
@@ -2567,48 +2607,46 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>76</v>
       </c>
@@ -2656,7 +2694,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2665,7 +2703,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>137</v>
@@ -2674,7 +2712,7 @@
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>76</v>
@@ -2683,16 +2721,16 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2705,23 +2743,25 @@
         <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2770,7 +2810,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2782,27 +2822,27 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2813,7 +2853,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2825,26 +2865,22 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>157</v>
-      </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q12" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
         <v>76</v>
       </c>
@@ -2888,13 +2924,13 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
@@ -2903,24 +2939,24 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AM12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN12" t="s" s="2">
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2928,7 +2964,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>86</v>
@@ -2943,24 +2979,26 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="O13" t="s" s="2">
+      <c r="P13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="P13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
         <v>76</v>
       </c>
@@ -3004,13 +3042,13 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
@@ -3019,24 +3057,24 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AM13" t="s" s="2">
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AN13" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3050,25 +3088,29 @@
         <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
       </c>
@@ -3116,50 +3158,50 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3171,17 +3213,15 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3218,37 +3258,37 @@
         <v>76</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3257,48 +3297,46 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>76</v>
       </c>
@@ -3322,63 +3360,63 @@
         <v>76</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3395,25 +3433,25 @@
         <v>76</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3438,13 +3476,13 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
@@ -3462,7 +3500,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3477,32 +3515,32 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>203</v>
+        <v>76</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>86</v>
@@ -3517,18 +3555,20 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>76</v>
       </c>
@@ -3576,7 +3616,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3591,35 +3631,35 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3631,16 +3671,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3690,13 +3730,13 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
@@ -3705,32 +3745,32 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
+      <c r="A20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>78</v>
@@ -3745,15 +3785,17 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3829,7 +3871,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>227</v>
       </c>
@@ -3857,7 +3899,7 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>228</v>
@@ -3935,18 +3977,18 @@
         <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>76</v>
+        <v>233</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3957,7 +3999,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -3969,7 +4011,7 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>235</v>
@@ -3978,9 +4020,7 @@
         <v>236</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>237</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
       </c>
@@ -4028,13 +4068,13 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
@@ -4043,24 +4083,24 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4068,10 +4108,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4083,19 +4123,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4144,13 +4182,13 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
@@ -4159,24 +4197,24 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4187,7 +4225,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4196,19 +4234,23 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
@@ -4256,50 +4298,50 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>76</v>
+        <v>255</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>175</v>
+        <v>256</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4311,17 +4353,15 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4358,37 +4398,37 @@
         <v>76</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4397,23 +4437,23 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4422,18 +4462,20 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4458,63 +4500,63 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AD26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>259</v>
+        <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4534,16 +4576,16 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4570,13 +4612,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4594,7 +4636,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4603,41 +4645,41 @@
         <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>76</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>76</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4649,17 +4691,15 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>133</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4708,19 +4748,19 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>76</v>
@@ -4735,23 +4775,23 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4763,15 +4803,17 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4781,7 +4823,7 @@
         <v>76</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>269</v>
+        <v>76</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>76</v>
@@ -4820,19 +4862,19 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>188</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
@@ -4847,12 +4889,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4872,23 +4914,19 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
@@ -4897,7 +4935,7 @@
         <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>76</v>
+        <v>277</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>76</v>
@@ -4936,7 +4974,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4948,27 +4986,27 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>278</v>
+        <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN30" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4985,25 +5023,25 @@
         <v>76</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5028,13 +5066,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5052,7 +5090,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5067,24 +5105,24 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5101,24 +5139,26 @@
         <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
       </c>
@@ -5142,13 +5182,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>76</v>
+        <v>294</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5181,24 +5221,24 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>175</v>
+        <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>76</v>
+        <v>297</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5221,15 +5261,17 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5278,7 +5320,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5293,24 +5335,24 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5321,7 +5363,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -5333,20 +5375,16 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
@@ -5394,13 +5432,13 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
@@ -5409,24 +5447,24 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>306</v>
+        <v>129</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN34" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5437,7 +5475,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5449,7 +5487,7 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>106</v>
+        <v>309</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>310</v>
@@ -5457,9 +5495,11 @@
       <c r="M35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5484,13 +5524,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>313</v>
+        <v>76</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>314</v>
+        <v>76</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5508,13 +5548,13 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
@@ -5523,24 +5563,24 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AN35" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5563,17 +5603,17 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5598,13 +5638,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>76</v>
+        <v>321</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5622,7 +5662,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5649,7 +5689,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>326</v>
       </c>
@@ -5665,7 +5705,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5674,7 +5714,7 @@
         <v>76</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>327</v>
@@ -5742,7 +5782,7 @@
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
@@ -5751,24 +5791,24 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5791,16 +5831,18 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
@@ -5848,7 +5890,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5863,24 +5905,24 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5891,7 +5933,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -5903,13 +5945,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>342</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>172</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>173</v>
+        <v>344</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5960,50 +6002,50 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>174</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>76</v>
+        <v>345</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>175</v>
+        <v>346</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6015,17 +6057,15 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -6074,25 +6114,25 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6101,16 +6141,16 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>343</v>
+        <v>145</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6123,26 +6163,24 @@
         <v>76</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>185</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>186</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
@@ -6190,7 +6228,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6208,7 +6246,7 @@
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6217,16 +6255,16 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6239,23 +6277,25 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>350</v>
+        <v>149</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6304,7 +6344,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6316,13 +6356,13 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>351</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6331,12 +6371,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6344,10 +6384,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6359,16 +6399,18 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>353</v>
+        <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
@@ -6392,13 +6434,13 @@
         <v>76</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>356</v>
+        <v>76</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>357</v>
+        <v>76</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>358</v>
+        <v>76</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>76</v>
@@ -6416,13 +6458,13 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
@@ -6434,16 +6476,16 @@
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>359</v>
+        <v>76</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>360</v>
       </c>
@@ -6456,7 +6498,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>86</v>
@@ -6471,18 +6513,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>363</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
       </c>
@@ -6506,13 +6546,13 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>76</v>
+        <v>364</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>76</v>
+        <v>365</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>76</v>
+        <v>366</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6533,7 +6573,7 @@
         <v>360</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>86</v>
@@ -6548,21 +6588,21 @@
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6585,16 +6625,18 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>241</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
       </c>
@@ -6642,7 +6684,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6660,21 +6702,21 @@
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>76</v>
+        <v>373</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6685,7 +6727,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -6697,20 +6739,16 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
       </c>
@@ -6734,13 +6772,13 @@
         <v>76</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>76</v>
@@ -6758,13 +6796,13 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>76</v>
@@ -6773,19 +6811,153 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>376</v>
+        <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>76</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN47">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI46">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
 </t>
   </si>
   <si>
-    <t>Requesting Clinician</t>
+    <t>Clinician User Index</t>
   </si>
   <si>
     <t>The user index for the person who is requesting or performing the service request.</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,6 +274,9 @@
     <t>Provider</t>
   </si>
   <si>
+    <t>administrative.individual</t>
+  </si>
+  <si>
     <t>Practitioner.id</t>
   </si>
   <si>
@@ -357,7 +360,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,6 +418,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -465,6 +472,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Practitioner.modifierExtension</t>
   </si>
   <si>
@@ -482,7 +493,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -583,76 +594,73 @@
     <t>Practitioner.name.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.3.0</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Practitioner.name.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Practitioner.name.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./NamePurpose</t>
-  </si>
-  <si>
-    <t>Practitioner.name.text</t>
-  </si>
-  <si>
     <t>Text representation of the full name</t>
   </si>
   <si>
@@ -840,10 +848,7 @@
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
-    <t>Telecommunications form for contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.3.0</t>
   </si>
   <si>
     <t>ContactPoint.system</t>
@@ -931,10 +936,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>Use of contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.3.0</t>
   </si>
   <si>
     <t>ContactPoint.use</t>
@@ -1021,7 +1023,7 @@
     <t>The gender of a person used for administrative purposes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
   </si>
   <si>
     <t>STF-5</t>
@@ -1091,6 +1093,10 @@
   </si>
   <si>
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>CER?</t>
@@ -1812,15 +1818,15 @@
         <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1831,7 +1837,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1840,19 +1846,19 @@
         <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1902,13 +1908,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1931,10 +1937,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1945,7 +1951,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>76</v>
@@ -1954,16 +1960,16 @@
         <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2014,19 +2020,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2043,10 +2049,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2057,28 +2063,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2128,19 +2134,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2157,10 +2163,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2171,7 +2177,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2183,16 +2189,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2218,13 +2224,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2242,19 +2248,19 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2271,21 +2277,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2297,16 +2303,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2356,25 +2362,25 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>76</v>
@@ -2385,14 +2391,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2411,16 +2417,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2470,7 +2476,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2482,13 +2488,13 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>76</v>
@@ -2499,10 +2505,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2510,7 +2516,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -2525,13 +2531,13 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2570,17 +2576,17 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2592,7 +2598,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2609,23 +2615,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>76</v>
@@ -2637,13 +2643,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2694,7 +2700,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2703,10 +2709,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2723,14 +2729,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2743,25 +2749,25 @@
         <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2810,7 +2816,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2822,13 +2828,13 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>76</v>
@@ -2839,10 +2845,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2862,20 +2868,20 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2924,7 +2930,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2936,27 +2942,27 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2967,7 +2973,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -2976,105 +2982,105 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="R13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="K13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3085,31 +3091,31 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -3158,7 +3164,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3170,16 +3176,16 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3187,10 +3193,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3201,7 +3207,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3213,13 +3219,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3270,13 +3276,13 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
@@ -3288,7 +3294,7 @@
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3299,14 +3305,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3325,16 +3331,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3372,19 +3378,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3396,13 +3402,13 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3413,10 +3419,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3427,31 +3433,31 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3476,13 +3482,11 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
@@ -3500,28 +3504,28 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3529,10 +3533,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3543,7 +3547,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3552,22 +3556,22 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3616,25 +3620,25 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -3645,21 +3649,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3668,19 +3672,19 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3730,28 +3734,28 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>76</v>
@@ -3759,18 +3763,18 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>78</v>
@@ -3782,19 +3786,19 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3844,7 +3848,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3856,16 +3860,16 @@
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -3873,10 +3877,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3896,16 +3900,16 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3956,7 +3960,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3968,16 +3972,16 @@
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -3985,10 +3989,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4008,16 +4012,16 @@
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4068,7 +4072,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4080,13 +4084,13 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4097,10 +4101,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4111,7 +4115,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4120,20 +4124,20 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4182,28 +4186,28 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4211,10 +4215,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4234,22 +4238,22 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4298,7 +4302,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4310,16 +4314,16 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4327,10 +4331,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4341,7 +4345,7 @@
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4353,13 +4357,13 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4410,13 +4414,13 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
@@ -4428,7 +4432,7 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4439,14 +4443,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4465,16 +4469,16 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4512,19 +4516,19 @@
         <v>76</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4536,13 +4540,13 @@
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4553,10 +4557,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4567,7 +4571,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4576,16 +4580,16 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4612,13 +4616,11 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4636,28 +4638,28 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4665,10 +4667,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4679,7 +4681,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4691,13 +4693,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4748,13 +4750,13 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>76</v>
@@ -4777,14 +4779,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4803,16 +4805,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4862,7 +4864,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4874,7 +4876,7 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
@@ -4891,10 +4893,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4905,7 +4907,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4917,13 +4919,13 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4935,7 +4937,7 @@
         <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>76</v>
@@ -4974,13 +4976,13 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
@@ -5003,10 +5005,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5017,7 +5019,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -5026,22 +5028,22 @@
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5090,28 +5092,28 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5119,10 +5121,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5133,31 +5135,31 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5182,11 +5184,9 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
         <v>294</v>
       </c>
@@ -5212,19 +5212,19 @@
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>297</v>
@@ -5249,7 +5249,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -5258,7 +5258,7 @@
         <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>299</v>
@@ -5326,19 +5326,19 @@
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5363,7 +5363,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -5372,10 +5372,10 @@
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>305</v>
@@ -5438,22 +5438,22 @@
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>76</v>
@@ -5484,7 +5484,7 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>309</v>
@@ -5560,7 +5560,7 @@
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>314</v>
@@ -5591,7 +5591,7 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5600,10 +5600,10 @@
         <v>76</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>318</v>
@@ -5638,7 +5638,7 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y36" t="s" s="2">
         <v>321</v>
@@ -5668,13 +5668,13 @@
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>323</v>
@@ -5705,7 +5705,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5714,7 +5714,7 @@
         <v>76</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>327</v>
@@ -5782,13 +5782,13 @@
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>331</v>
@@ -5902,7 +5902,7 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>76</v>
@@ -6014,16 +6014,16 @@
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>345</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6045,7 +6045,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6057,13 +6057,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6114,13 +6114,13 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
@@ -6132,7 +6132,7 @@
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6143,14 +6143,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6169,16 +6169,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6228,7 +6228,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6240,13 +6240,13 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6257,14 +6257,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6277,25 +6277,25 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6344,7 +6344,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6356,13 +6356,13 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6399,17 +6399,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6458,7 +6458,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6470,13 +6470,13 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6498,10 +6498,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6513,13 +6513,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6546,13 +6546,13 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6570,28 +6570,28 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6613,7 +6613,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>76</v>
@@ -6625,17 +6625,17 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6684,28 +6684,28 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6727,7 +6727,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -6739,13 +6739,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6796,25 +6796,25 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6825,10 +6825,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6851,19 +6851,19 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6888,13 +6888,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6912,7 +6912,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6924,16 +6924,16 @@
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>76</v>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,9 +274,6 @@
     <t>Provider</t>
   </si>
   <si>
-    <t>administrative.individual</t>
-  </si>
-  <si>
     <t>Practitioner.id</t>
   </si>
   <si>
@@ -360,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -418,10 +415,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -472,10 +465,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Practitioner.modifierExtension</t>
   </si>
   <si>
@@ -493,7 +482,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -594,73 +583,76 @@
     <t>Practitioner.name.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Practitioner.name.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.3.0</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./NamePurpose</t>
-  </si>
-  <si>
-    <t>Practitioner.name.text</t>
-  </si>
-  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Practitioner.name.text</t>
+  </si>
+  <si>
     <t>Text representation of the full name</t>
   </si>
   <si>
@@ -848,7 +840,10 @@
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.3.0</t>
+    <t>Telecommunications form for contact point.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
   </si>
   <si>
     <t>ContactPoint.system</t>
@@ -936,7 +931,10 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.3.0</t>
+    <t>Use of contact point.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
   </si>
   <si>
     <t>ContactPoint.use</t>
@@ -1023,7 +1021,7 @@
     <t>The gender of a person used for administrative purposes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>STF-5</t>
@@ -1093,10 +1091,6 @@
   </si>
   <si>
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>CER?</t>
@@ -1818,15 +1812,15 @@
         <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1837,28 +1831,28 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1908,13 +1902,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1937,10 +1931,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1951,25 +1945,25 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2020,19 +2014,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2049,10 +2043,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2063,28 +2057,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2134,19 +2128,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2163,10 +2157,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2177,7 +2171,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2189,16 +2183,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2224,43 +2218,43 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2277,21 +2271,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2303,16 +2297,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2362,25 +2356,25 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>76</v>
@@ -2391,14 +2385,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2417,16 +2411,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2476,7 +2470,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2488,13 +2482,13 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>76</v>
@@ -2505,10 +2499,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2516,7 +2510,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -2531,13 +2525,13 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2576,17 +2570,17 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2598,7 +2592,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2615,23 +2609,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>76</v>
@@ -2643,13 +2637,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2700,7 +2694,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2709,10 +2703,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2729,14 +2723,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2749,25 +2743,25 @@
         <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2816,7 +2810,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2828,13 +2822,13 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>76</v>
@@ -2845,10 +2839,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2868,20 +2862,20 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2930,7 +2924,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2942,27 +2936,27 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2973,114 +2967,114 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="P13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="R13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="O13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3091,31 +3085,31 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -3164,7 +3158,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3176,16 +3170,16 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3193,10 +3187,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3207,7 +3201,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3219,13 +3213,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3276,13 +3270,13 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
@@ -3294,7 +3288,7 @@
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3305,14 +3299,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3331,16 +3325,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3378,19 +3372,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3402,13 +3396,13 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3419,10 +3413,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3433,31 +3427,31 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3482,50 +3476,52 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Y17" s="2"/>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3533,10 +3529,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3547,31 +3543,31 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3620,25 +3616,25 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -3649,42 +3645,42 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3734,28 +3730,28 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>76</v>
@@ -3763,18 +3759,18 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>78</v>
@@ -3786,19 +3782,19 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3848,7 +3844,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3860,16 +3856,16 @@
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -3877,10 +3873,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3900,16 +3896,16 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3960,7 +3956,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3972,16 +3968,16 @@
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -3989,10 +3985,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4012,16 +4008,16 @@
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4072,7 +4068,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4084,13 +4080,13 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4101,10 +4097,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4115,29 +4111,29 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4186,28 +4182,28 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4215,10 +4211,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4238,22 +4234,22 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4302,7 +4298,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4314,16 +4310,16 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4331,10 +4327,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4345,7 +4341,7 @@
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4357,13 +4353,13 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4414,13 +4410,13 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
@@ -4432,7 +4428,7 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4443,14 +4439,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4469,16 +4465,16 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4516,19 +4512,19 @@
         <v>76</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4540,13 +4536,13 @@
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4557,10 +4553,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4571,25 +4567,25 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4616,50 +4612,52 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="Z27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI27" t="s" s="2">
+      <c r="AJ27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4667,10 +4665,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4681,7 +4679,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4693,13 +4691,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4750,13 +4748,13 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>76</v>
@@ -4779,14 +4777,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4805,16 +4803,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4864,7 +4862,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4876,7 +4874,7 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
@@ -4893,10 +4891,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4907,7 +4905,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4919,13 +4917,13 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4937,52 +4935,52 @@
         <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="T30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
@@ -5005,10 +5003,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5019,31 +5017,31 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5092,28 +5090,28 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5121,10 +5119,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5135,31 +5133,31 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5184,9 +5182,11 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="Z32" t="s" s="2">
         <v>294</v>
       </c>
@@ -5212,19 +5212,19 @@
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>297</v>
@@ -5249,16 +5249,16 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>299</v>
@@ -5326,19 +5326,19 @@
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5363,19 +5363,19 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>305</v>
@@ -5438,22 +5438,22 @@
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>76</v>
@@ -5484,7 +5484,7 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>309</v>
@@ -5560,7 +5560,7 @@
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>314</v>
@@ -5591,19 +5591,19 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>318</v>
@@ -5638,7 +5638,7 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y36" t="s" s="2">
         <v>321</v>
@@ -5668,13 +5668,13 @@
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>323</v>
@@ -5705,16 +5705,16 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>327</v>
@@ -5782,13 +5782,13 @@
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>331</v>
@@ -5902,7 +5902,7 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>76</v>
@@ -6014,16 +6014,16 @@
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AK39" t="s" s="2">
+      <c r="AL39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6045,7 +6045,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6057,13 +6057,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6114,13 +6114,13 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
@@ -6132,7 +6132,7 @@
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6143,14 +6143,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6169,16 +6169,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6228,7 +6228,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6240,13 +6240,13 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6257,14 +6257,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6277,25 +6277,25 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6344,7 +6344,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6356,13 +6356,13 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6399,17 +6399,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6458,7 +6458,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6470,13 +6470,13 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6498,10 +6498,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6513,13 +6513,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6546,52 +6546,52 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Y44" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Y44" t="s" s="2">
+      <c r="Z44" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z44" t="s" s="2">
+      <c r="AA44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6613,7 +6613,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>76</v>
@@ -6625,17 +6625,17 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6684,28 +6684,28 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6727,7 +6727,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -6739,13 +6739,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6796,25 +6796,25 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6825,10 +6825,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6851,19 +6851,19 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6888,14 +6888,14 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y47" t="s" s="2">
+      <c r="Z47" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6924,16 +6924,16 @@
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>76</v>

--- a/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
